--- a/docs/APIDocs/excel2img/examples/additional/inputs/wide-table.xlsx
+++ b/docs/APIDocs/excel2img/examples/additional/inputs/wide-table.xlsx
@@ -7,11 +7,11 @@
   </bookViews>
   <sheets>
     <sheet name="24列の横長一覧" r:id="rId3" sheetId="1"/>
-    <sheet name="48列・可読性不足" r:id="rId4" sheetId="2"/>
+    <sheet name="48列・横分割" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'24列の横長一覧'!$A$1:$X$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'48列・可読性不足'!$A$1:$AV$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'48列・横分割'!$A$1:$AV$29</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -25,7 +25,7 @@
     <t>地域別の月次処理一覧 / 24列を横幅に収めるサンプル</t>
   </si>
   <si>
-    <t>架空の検証データ  |  20拠点 × 7か月  |  各セル11pt以上  |  横方向の分割なし</t>
+    <t>架空の検証データ  |  20拠点 × 7か月  |  各セル11pt以上  |  必要に応じて縮小と横分割</t>
   </si>
   <si>
     <t>基本情報</t>
@@ -209,13 +209,13 @@
   </si>
   <si>
     <t>確認ポイント：月ごとの結合見出し、交互の行色、罫線、右寄せの数値を同じ横長ページで確認できます。
-次の「48列・可読性不足」シートは意図的に広く、既定の最小文字サイズを満たさずスキップされる比較用です。</t>
-  </si>
-  <si>
-    <t>比較用 / 48列は横幅を縮小すると11ptの文字が読みにくくなる</t>
-  </si>
-  <si>
-    <t>このシートは既定設定で WIDTH_UNREADABLE としてスキップされる想定です。</t>
+次の「48列・横分割」シートは意図的に広く、文字を小さくし過ぎず複数ページへ横分割する比較用です。</t>
+  </si>
+  <si>
+    <t>横分割の比較 / 48列を読める文字サイズのまま複数ページへ</t>
+  </si>
+  <si>
+    <t>文字の可読性を保てる倍率まで縮小し、それでも広い範囲は左から右へ分割して出力します。</t>
   </si>
   <si>
     <t>項目</t>
@@ -677,7 +677,7 @@
     <t>195</t>
   </si>
   <si>
-    <t>確認ポイント：無理に小さな画像にせず、この範囲をスキップして他の読めるシートは出力します。</t>
+    <t>確認ポイント：ページの左右を順につなぐと元の横長範囲になります。端の列、結合見出し、画像の位置も比較します。</t>
   </si>
 </sst>
 </file>
